--- a/app/static/templates/excel/template_exams.xlsx
+++ b/app/static/templates/excel/template_exams.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Exams" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exams" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/app/static/templates/excel/template_exams.xlsx
+++ b/app/static/templates/excel/template_exams.xlsx
@@ -449,22 +449,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="43" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="37" customWidth="1" min="9" max="9"/>
+    <col width="43" customWidth="1" min="10" max="10"/>
+    <col width="38" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="45" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,37 +503,52 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>question_text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>option_a</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>option_b</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>option_c</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>option_d</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>correct_answer</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>explanation</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>media_url</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>transcript</t>
         </is>
       </c>
     </row>
@@ -567,39 +585,46 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>SINGLE_CHOICE</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>All employees are requested to submit their expense reports _______ Friday afternoon.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>by</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>until</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>'By Friday afternoon' nghĩa là trước hoặc muộn nhất vào chiều thứ Sáu (deadline). 'Until' chỉ hành động kéo dài liên tục.</t>
         </is>
       </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -634,104 +659,126 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>SINGLE_CHOICE</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Mr. Henderson was _______ promoted to Senior Marketing Director.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>recent</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>recently</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>more recent</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>recency</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Vị trí đứng giữa trợ động từ 'was' và phân từ hai 'promoted' cần một trạng từ (Adverb) để bổ nghĩa -&gt; chọn 'recently'.</t>
         </is>
       </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IELTS</t>
+          <t>TOEIC</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>IELTS General Practice Test 01</t>
+          <t>TOEIC Listening Practice Test 01</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>READING</t>
+          <t>LISTENING</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>Part 1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>According to the notice, what must visitors do before entering the construction area?</t>
+          <t>SINGLE_CHOICE</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Sign the guestbook</t>
+          <t>Look at the picture and choose the best statement.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Wear a hard hat and safety vest</t>
+          <t>The woman is typing on a laptop.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Call their supervisor</t>
+          <t>The woman is drinking a cup of coffee.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Leave their mobile phones at reception</t>
+          <t>The woman is walking in the park.</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>The woman is reading a printed magazine.</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Đoạn văn quy định rõ tất cả khách tham quan bắt buộc phải trang bị mũ bảo hộ và áo phản quang trước khi bước vào công trường.</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Bức tranh mô tả một người phụ nữ đang ngồi gõ bàn phím máy tính xách tay trong văn phòng.</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://actions.google.com/sounds/v1/office/typing_on_computer_keyboard.ogg</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>The woman is sitting at her desk typing on a laptop computer.</t>
         </is>
       </c>
     </row>
